--- a/artfynd/A 24057-2025 artfynd.xlsx
+++ b/artfynd/A 24057-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117772745</v>
+        <v>117772742</v>
       </c>
       <c r="B2" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593114</v>
+        <v>593259</v>
       </c>
       <c r="R2" t="n">
-        <v>6971416</v>
+        <v>6971227</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,12 +775,7 @@
         <v>117772744</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117772742</v>
+        <v>117863976</v>
       </c>
       <c r="B4" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593259</v>
+        <v>593486</v>
       </c>
       <c r="R4" t="n">
-        <v>6971227</v>
+        <v>6970928</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Noel Wieser</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Noel Wieser</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117772743</v>
+        <v>117772745</v>
       </c>
       <c r="B5" t="n">
-        <v>56272</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208260</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593369</v>
+        <v>593114</v>
       </c>
       <c r="R5" t="n">
-        <v>6971085</v>
+        <v>6971416</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117863976</v>
+        <v>117772743</v>
       </c>
       <c r="B6" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>208260</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593486</v>
+        <v>593369</v>
       </c>
       <c r="R6" t="n">
-        <v>6970928</v>
+        <v>6971085</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,12 +1148,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Noel Wieser</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Noel Wieser</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 24057-2025 artfynd.xlsx
+++ b/artfynd/A 24057-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117772742</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117772744</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117863976</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117772745</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,8 +1182,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117772743</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>